--- a/outputs/51431.xlsx
+++ b/outputs/51431.xlsx
@@ -104,8 +104,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -301,23 +305,23 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="str">
-        <f aca="false">TRIM(MID(SUBSTITUTE(A2,";",REPT(" ",100)),1,100))</f>
+      <c r="B2" s="1" t="str">
+        <f aca="false">LEFT(A2, FIND(";", A2)-1)</f>
         <v>Nizghi, Righat</v>
       </c>
     </row>

--- a/outputs/51431.xlsx
+++ b/outputs/51431.xlsx
@@ -321,7 +321,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="str">
-        <f aca="false">LEFT(A2, FIND(";", A2)-1)</f>
+        <f aca="false">LEFT(A2,FIND(";",A2)-1)</f>
         <v>Nizghi, Righat</v>
       </c>
     </row>
